--- a/.cloud_chaos_data/game_selections_backup.xlsx
+++ b/.cloud_chaos_data/game_selections_backup.xlsx
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -424,162 +424,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/.cloud_chaos_data/game_selections_backup.xlsx
+++ b/.cloud_chaos_data/game_selections_backup.xlsx
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -424,6 +424,162 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
